--- a/astro-site/public/dl/kit-escandallos/07-cafeteria-brunch.xlsx
+++ b/astro-site/public/dl/kit-escandallos/07-cafeteria-brunch.xlsx
@@ -24,7 +24,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Eggs Benedict'!$A$1:$J$36</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Carrot Cake'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Carrot Cake'!$A$1:$J$37</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Conversiones'!$A$1:$J$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Conversiones'!$A$1:$J$67</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'Mermas'!$A$1:$J$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -989,7 +989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B64"/>
+  <dimension ref="A1:B65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1101,256 +1101,263 @@
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>▸ Cantidad: la que usas en el plato, EN LA UNIDAD DE USO.</t>
+          <t>▸ ¿Llevas tus precios en la plantilla 13 (Lista de Precios de Ingredientes)? Lleva su «Precio por unidad base» a «Precio/Ud (€)» con Pegado especial → Valores (en Excel, Ctrl+Alt+V y luego V) y pon esa misma unidad en «Ud. Compra». Un pegado normal arrastraría la fórmula: el precio y el coste de esa línea se quedarían en blanco sin avisar, y el coste del plato saldría más bajo.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>▸ Ud. Uso: la unidad en la que mides al cocinar (g, ml, cl, ud…).</t>
+          <t>▸ Cantidad: la que usas en el plato, EN LA UNIDAD DE USO.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>▸ Factor: conversión automática Ud. Compra → Ud. Uso, de la hoja «Conversiones». Si la pareja NO está en la tabla, el Factor se pone en rojo con un «?» y el Coste dice «revisa unidades»: añade la equivalencia en «Conversiones» antes de fiarte del número. Nunca da un coste plausible y falso.</t>
+          <t>▸ Ud. Uso: la unidad en la que mides al cocinar (g, ml, cl, ud…).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>▸ Merma (%): desperdicio. En las filas de ejemplo está escrita a mano; en las vacías la trae la hoja «Mermas» en cuanto eliges categoría, y puedes escribir encima.</t>
+          <t>▸ Factor: conversión automática Ud. Compra → Ud. Uso, de la hoja «Conversiones». Si la pareja NO está en la tabla, el Factor se pone en rojo con un «?» y el Coste dice «revisa unidades»: añade la equivalencia en «Conversiones» antes de fiarte del número. Nunca da un coste plausible y falso.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>▸ Ojo con la merma cuando mides en PIEZAS: la del 11 % de los huevos es la CÁSCARA, y sólo tiene sentido sobre el peso. Si compras y mides en unidades, déjala en 0 %: seis huevos son seis huevos, no 6,74. La misma regla vale para cualquier ingrediente que cuentes por unidad.</t>
+          <t>▸ Merma (%): desperdicio. En las filas de ejemplo está escrita a mano; en las vacías la trae la hoja «Mermas» en cuanto eliges categoría, y puedes escribir encima.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>▸ Cant. Bruta: lo que hay que comprar contando la merma (automático).</t>
+          <t>▸ Ojo con la merma cuando mides en PIEZAS: la del 11 % de los huevos es la CÁSCARA, y sólo tiene sentido sobre el peso. Si compras y mides en unidades, déjala en 0 %: seis huevos son seis huevos, no 6,74. La misma regla vale para cualquier ingrediente que cuentes por unidad.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="6" t="inlineStr">
         <is>
+          <t>▸ Cant. Bruta: lo que hay que comprar contando la merma (automático).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="6" t="inlineStr">
+        <is>
           <t>▸ Coste (€): Cant. Bruta × Precio/Ud ÷ Factor (automático).</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="B27" s="4" t="inlineStr">
+    <row r="27"/>
+    <row r="28">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Bloque de resultado</t>
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>▸ Coste elaboración (%): recargo sobre la materia prima para cubrir energía, envasado y pérdidas de preparación que no se escandallan línea a línea. Viene al 10 %; ponlo a 0 % si prefieres imputar esos costes aparte.</t>
-        </is>
-      </c>
-    </row>
+    <row r="29"/>
     <row r="30">
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>▸ COSTE TOTAL DEL PLATO: materia prima + coste de elaboración.</t>
+          <t>▸ Coste elaboración (%): recargo sobre la materia prima para cubrir energía, envasado y pérdidas de preparación que no se escandallan línea a línea. Viene al 10 %; ponlo a 0 % si prefieres imputar esos costes aparte.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>▸ Nº de raciones: cuántas raciones salen de lo escandallado. Déjalo en 1 si es un plato individual.</t>
+          <t>▸ COSTE TOTAL DEL PLATO: materia prima + coste de elaboración.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>▸ COSTE POR RACIÓN: coste total ÷ raciones. Es la base del PVP.</t>
+          <t>▸ Nº de raciones: cuántas raciones salen de lo escandallado. Déjalo en 1 si es un plato individual.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>▸ Food Cost objetivo (%): el que quieres conseguir. PVP sin IVA = coste por ración ÷ food cost objetivo.</t>
+          <t>▸ COSTE POR RACIÓN: coste total ÷ raciones. Es la base del PVP.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>▸ Tipo de IVA (%): editable. 10 % en hostelería en España; cámbialo si te aplica otro tipo (IGIC en Canarias, o el IVA/ITBIS/IVU de tu país en Latinoamérica).</t>
+          <t>▸ Food Cost objetivo (%): el que quieres conseguir. PVP sin IVA = coste por ración ÷ food cost objetivo.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>▸ PVP actual en carta (sin IVA): lo que cobras HOY. Déjalo vacío si todavía no lo tienes.</t>
+          <t>▸ Tipo de IVA (%): editable. 10 % en hostelería en España; cámbialo si te aplica otro tipo (IGIC en Canarias, o el IVA/ITBIS/IVU de tu país en Latinoamérica).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="6" t="inlineStr">
         <is>
+          <t>▸ PVP actual en carta (sin IVA): lo que cobras HOY. Déjalo vacío si todavía no lo tienes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="6" t="inlineStr">
+        <is>
           <t>▸ FOOD COST REAL (%): coste por ración ÷ PVP actual. Se pone en rojo en cuanto supera tu objetivo.</t>
         </is>
       </c>
     </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="B38" s="4" t="inlineStr">
+    <row r="38"/>
+    <row r="39">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Hojas auxiliares</t>
         </is>
       </c>
     </row>
-    <row r="39"/>
-    <row r="40">
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>▸ «Conversiones»: equivalencias Ud. Compra → Ud. Uso. Va SIN protección: añade las parejas que te falten y corrige el tamaño de los formatos (la botella viene a 70 cl y la lata a 33 cl; si tu vino es de 75 cl, cambia el 70 por 75 en «botella→cl»).</t>
-        </is>
-      </c>
-    </row>
+    <row r="40"/>
     <row r="41">
       <c r="B41" s="6" t="inlineStr">
         <is>
+          <t>▸ «Conversiones»: equivalencias Ud. Compra → Ud. Uso. Va SIN protección: añade las parejas que te falten y corrige el tamaño de los formatos (la botella viene a 70 cl y la lata a 33 cl; si tu vino es de 75 cl, cambia el 70 por 75 en «botella→cl»).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="6" t="inlineStr">
+        <is>
           <t>▸ «Mermas»: merma mínima, típica y máxima por categoría. La típica es la que se precarga en las filas vacías.</t>
         </is>
       </c>
     </row>
-    <row r="42"/>
-    <row r="43">
-      <c r="B43" s="4" t="inlineStr">
+    <row r="43"/>
+    <row r="44">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>Protección de la hoja</t>
         </is>
       </c>
     </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>▸ Las hojas están protegidas SIN contraseña para que no borres una fórmula sin querer: sólo se escriben las celdas verdes.</t>
-        </is>
-      </c>
-    </row>
+    <row r="45"/>
     <row r="46">
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>▸ Para tocar cualquier otra cosa —insertar filas, pegar la foto del plato, cambiar una fórmula—: Revisar → Desproteger hoja. No pide contraseña.</t>
+          <t>▸ Las hojas están protegidas SIN contraseña para que no borres una fórmula sin querer: sólo se escriben las celdas verdes.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>▸ Si te quedas sin filas: desprotege la hoja e inserta filas DENTRO del bloque de ingredientes (clic derecho sobre una fila del bloque → Insertar), nunca debajo de la última. Así el «COSTE TOTAL INGREDIENTES» las recoge solo; lo que escribas por debajo del bloque NO suma.</t>
+          <t>▸ Para tocar cualquier otra cosa —insertar filas, pegar la foto del plato, cambiar una fórmula—: Revisar → Desproteger hoja. No pide contraseña.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="6" t="inlineStr">
         <is>
+          <t>▸ Si te quedas sin filas: desprotege la hoja e inserta filas DENTRO del bloque de ingredientes (clic derecho sobre una fila del bloque → Insertar), nunca debajo de la última. Así el «COSTE TOTAL INGREDIENTES» las recoge solo; lo que escribas por debajo del bloque NO suma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="6" t="inlineStr">
+        <is>
           <t>▸ La foto del plato NO se puede arrastrar con la hoja protegida: primero Revisar → Desproteger hoja, y después Insertar → Imagen.</t>
         </is>
       </c>
     </row>
-    <row r="49"/>
-    <row r="50">
-      <c r="B50" s="4" t="inlineStr">
+    <row r="50"/>
+    <row r="51">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>Referencia de mermas estándar</t>
         </is>
       </c>
     </row>
-    <row r="51"/>
-    <row r="52">
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>▸ Carne roja 20 % | Aves 25 % | Pescado 35 % | Marisco 45 %</t>
-        </is>
-      </c>
-    </row>
+    <row r="52"/>
     <row r="53">
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>▸ Verdura hoja 25 % | Verdura raíz 12 % | Verdura fruto 10 % | Fruta 15 %</t>
+          <t>▸ Carne roja 20 % | Aves 25 % | Pescado 35 % | Marisco 45 %</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>▸ Lácteos 3 % | Secos/granos 2 % | Congelados 7 % | Pan/bollería 5 %</t>
+          <t>▸ Verdura hoja 25 % | Verdura raíz 12 % | Verdura fruto 10 % | Fruta 15 %</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>▸ Huevos 11 % | Aceites/grasas 3 % | Especias/hierbas 20 % | Chocolate/cacao 5 %</t>
+          <t>▸ Lácteos 3 % | Secos/granos 2 % | Congelados 7 % | Pan/bollería 5 %</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>▸ Bebidas/licores 2 % | Setas/hongos 20 % | Conservas/encurtidos 8 % | Salsas/condimentos 5 %</t>
+          <t>▸ Huevos 11 % | Aceites/grasas 3 % | Especias/hierbas 20 % | Chocolate/cacao 5 %</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>▸ Pasta/arroz 2 %</t>
+          <t>▸ Bebidas/licores 2 % | Setas/hongos 20 % | Conservas/encurtidos 8 % | Salsas/condimentos 5 %</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="6" t="inlineStr">
         <is>
+          <t>▸ Pasta/arroz 2 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="6" t="inlineStr">
+        <is>
           <t>▸ Son las 21 categorías del desplegable. La tabla completa, con mínimo y máximo, está en la hoja «Mermas».</t>
         </is>
       </c>
     </row>
-    <row r="59"/>
-    <row r="60">
-      <c r="B60" s="6" t="inlineStr">
+    <row r="60"/>
+    <row r="61">
+      <c r="B61" s="6" t="inlineStr">
         <is>
           <t>— Kit de Escandallos Pro · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
-    <row r="61"/>
-    <row r="62">
-      <c r="B62" s="6" t="inlineStr">
+    <row r="62"/>
+    <row r="63">
+      <c r="B63" s="6" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · Todos los derechos reservados</t>
         </is>
       </c>
     </row>
-    <row r="63"/>
-    <row r="64">
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-escandallos · info@aichef.pro</t>
+    <row r="64"/>
+    <row r="65">
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>Versión 2.1 · septiembre 2026 · aichef.pro/kit-escandallos · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1507,7 @@
         </is>
       </c>
       <c r="G5" s="56">
-        <f>IF(C5&amp;F5="","",IFERROR(VLOOKUP(C5&amp;"→"&amp;F5,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C5&amp;F5="","",IFERROR(VLOOKUP(C5&amp;"→"&amp;F5,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H5" s="57" t="n">
@@ -1545,7 +1552,7 @@
         </is>
       </c>
       <c r="G6" s="56">
-        <f>IF(C6&amp;F6="","",IFERROR(VLOOKUP(C6&amp;"→"&amp;F6,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C6&amp;F6="","",IFERROR(VLOOKUP(C6&amp;"→"&amp;F6,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H6" s="57" t="n">
@@ -1590,7 +1597,7 @@
         </is>
       </c>
       <c r="G7" s="56">
-        <f>IF(C7&amp;F7="","",IFERROR(VLOOKUP(C7&amp;"→"&amp;F7,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C7&amp;F7="","",IFERROR(VLOOKUP(C7&amp;"→"&amp;F7,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>12.0</v>
       </c>
       <c r="H7" s="57" t="n">
@@ -1635,7 +1642,7 @@
         </is>
       </c>
       <c r="G8" s="56">
-        <f>IF(C8&amp;F8="","",IFERROR(VLOOKUP(C8&amp;"→"&amp;F8,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C8&amp;F8="","",IFERROR(VLOOKUP(C8&amp;"→"&amp;F8,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H8" s="57" t="n">
@@ -1686,7 +1693,7 @@
         </is>
       </c>
       <c r="G9" s="56">
-        <f>IF(C9&amp;F9="","",IFERROR(VLOOKUP(C9&amp;"→"&amp;F9,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C9&amp;F9="","",IFERROR(VLOOKUP(C9&amp;"→"&amp;F9,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H9" s="57" t="n">
@@ -1731,7 +1738,7 @@
         </is>
       </c>
       <c r="G10" s="56">
-        <f>IF(C10&amp;F10="","",IFERROR(VLOOKUP(C10&amp;"→"&amp;F10,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C10&amp;F10="","",IFERROR(VLOOKUP(C10&amp;"→"&amp;F10,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H10" s="57" t="n">
@@ -1776,7 +1783,7 @@
         </is>
       </c>
       <c r="G11" s="56">
-        <f>IF(C11&amp;F11="","",IFERROR(VLOOKUP(C11&amp;"→"&amp;F11,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C11&amp;F11="","",IFERROR(VLOOKUP(C11&amp;"→"&amp;F11,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H11" s="57" t="n">
@@ -1801,7 +1808,7 @@
       <c r="E12" s="58" t="n"/>
       <c r="F12" s="58" t="n"/>
       <c r="G12" s="56">
-        <f>IF(C12&amp;F12="","",IFERROR(VLOOKUP(C12&amp;"→"&amp;F12,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C12&amp;F12="","",IFERROR(VLOOKUP(C12&amp;"→"&amp;F12,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H12" s="59">
@@ -1827,7 +1834,7 @@
       <c r="E13" s="58" t="n"/>
       <c r="F13" s="58" t="n"/>
       <c r="G13" s="56">
-        <f>IF(C13&amp;F13="","",IFERROR(VLOOKUP(C13&amp;"→"&amp;F13,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C13&amp;F13="","",IFERROR(VLOOKUP(C13&amp;"→"&amp;F13,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H13" s="59">
@@ -1853,7 +1860,7 @@
       <c r="E14" s="58" t="n"/>
       <c r="F14" s="58" t="n"/>
       <c r="G14" s="56">
-        <f>IF(C14&amp;F14="","",IFERROR(VLOOKUP(C14&amp;"→"&amp;F14,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C14&amp;F14="","",IFERROR(VLOOKUP(C14&amp;"→"&amp;F14,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H14" s="59">
@@ -1879,7 +1886,7 @@
       <c r="E15" s="58" t="n"/>
       <c r="F15" s="58" t="n"/>
       <c r="G15" s="56">
-        <f>IF(C15&amp;F15="","",IFERROR(VLOOKUP(C15&amp;"→"&amp;F15,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C15&amp;F15="","",IFERROR(VLOOKUP(C15&amp;"→"&amp;F15,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H15" s="59">
@@ -1904,7 +1911,7 @@
       <c r="E16" s="58" t="n"/>
       <c r="F16" s="58" t="n"/>
       <c r="G16" s="56">
-        <f>IF(C16&amp;F16="","",IFERROR(VLOOKUP(C16&amp;"→"&amp;F16,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C16&amp;F16="","",IFERROR(VLOOKUP(C16&amp;"→"&amp;F16,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H16" s="59">
@@ -1928,7 +1935,7 @@
       <c r="E17" s="58" t="n"/>
       <c r="F17" s="58" t="n"/>
       <c r="G17" s="56">
-        <f>IF(C17&amp;F17="","",IFERROR(VLOOKUP(C17&amp;"→"&amp;F17,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C17&amp;F17="","",IFERROR(VLOOKUP(C17&amp;"→"&amp;F17,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H17" s="59">
@@ -1952,7 +1959,7 @@
       <c r="E18" s="58" t="n"/>
       <c r="F18" s="58" t="n"/>
       <c r="G18" s="56">
-        <f>IF(C18&amp;F18="","",IFERROR(VLOOKUP(C18&amp;"→"&amp;F18,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C18&amp;F18="","",IFERROR(VLOOKUP(C18&amp;"→"&amp;F18,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H18" s="59">
@@ -1976,7 +1983,7 @@
       <c r="E19" s="58" t="n"/>
       <c r="F19" s="58" t="n"/>
       <c r="G19" s="56">
-        <f>IF(C19&amp;F19="","",IFERROR(VLOOKUP(C19&amp;"→"&amp;F19,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C19&amp;F19="","",IFERROR(VLOOKUP(C19&amp;"→"&amp;F19,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H19" s="59">
@@ -2000,7 +2007,7 @@
       <c r="E20" s="58" t="n"/>
       <c r="F20" s="58" t="n"/>
       <c r="G20" s="56">
-        <f>IF(C20&amp;F20="","",IFERROR(VLOOKUP(C20&amp;"→"&amp;F20,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C20&amp;F20="","",IFERROR(VLOOKUP(C20&amp;"→"&amp;F20,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H20" s="59">
@@ -2024,7 +2031,7 @@
       <c r="E21" s="58" t="n"/>
       <c r="F21" s="58" t="n"/>
       <c r="G21" s="56">
-        <f>IF(C21&amp;F21="","",IFERROR(VLOOKUP(C21&amp;"→"&amp;F21,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C21&amp;F21="","",IFERROR(VLOOKUP(C21&amp;"→"&amp;F21,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H21" s="59">
@@ -2288,23 +2295,23 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="18">
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="A23:I23"/>
     <mergeCell ref="A25:I25"/>
-    <mergeCell ref="L8:M9"/>
-    <mergeCell ref="A33:I33"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="A37:I37"/>
-    <mergeCell ref="L15:M15"/>
-    <mergeCell ref="A27:I27"/>
-    <mergeCell ref="A23:I23"/>
     <mergeCell ref="A34:I34"/>
     <mergeCell ref="A30:I30"/>
     <mergeCell ref="A31:H31"/>
     <mergeCell ref="A36:H36"/>
+    <mergeCell ref="L8:M9"/>
     <mergeCell ref="A32:I32"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A26:H26"/>
     <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A33:I33"/>
     <mergeCell ref="A24:H24"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="A27:I27"/>
     <mergeCell ref="A1:J1"/>
   </mergeCells>
   <conditionalFormatting sqref="G5:G21">
@@ -2467,7 +2474,7 @@
         </is>
       </c>
       <c r="G5" s="56">
-        <f>IF(C5&amp;F5="","",IFERROR(VLOOKUP(C5&amp;"→"&amp;F5,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C5&amp;F5="","",IFERROR(VLOOKUP(C5&amp;"→"&amp;F5,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H5" s="57" t="n">
@@ -2512,7 +2519,7 @@
         </is>
       </c>
       <c r="G6" s="56">
-        <f>IF(C6&amp;F6="","",IFERROR(VLOOKUP(C6&amp;"→"&amp;F6,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C6&amp;F6="","",IFERROR(VLOOKUP(C6&amp;"→"&amp;F6,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H6" s="57" t="n">
@@ -2557,7 +2564,7 @@
         </is>
       </c>
       <c r="G7" s="56">
-        <f>IF(C7&amp;F7="","",IFERROR(VLOOKUP(C7&amp;"→"&amp;F7,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C7&amp;F7="","",IFERROR(VLOOKUP(C7&amp;"→"&amp;F7,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H7" s="57" t="n">
@@ -2602,7 +2609,7 @@
         </is>
       </c>
       <c r="G8" s="56">
-        <f>IF(C8&amp;F8="","",IFERROR(VLOOKUP(C8&amp;"→"&amp;F8,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C8&amp;F8="","",IFERROR(VLOOKUP(C8&amp;"→"&amp;F8,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H8" s="57" t="n">
@@ -2653,7 +2660,7 @@
         </is>
       </c>
       <c r="G9" s="56">
-        <f>IF(C9&amp;F9="","",IFERROR(VLOOKUP(C9&amp;"→"&amp;F9,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C9&amp;F9="","",IFERROR(VLOOKUP(C9&amp;"→"&amp;F9,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H9" s="57" t="n">
@@ -2698,7 +2705,7 @@
         </is>
       </c>
       <c r="G10" s="56">
-        <f>IF(C10&amp;F10="","",IFERROR(VLOOKUP(C10&amp;"→"&amp;F10,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C10&amp;F10="","",IFERROR(VLOOKUP(C10&amp;"→"&amp;F10,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H10" s="57" t="n">
@@ -2743,7 +2750,7 @@
         </is>
       </c>
       <c r="G11" s="56">
-        <f>IF(C11&amp;F11="","",IFERROR(VLOOKUP(C11&amp;"→"&amp;F11,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C11&amp;F11="","",IFERROR(VLOOKUP(C11&amp;"→"&amp;F11,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H11" s="57" t="n">
@@ -2768,7 +2775,7 @@
       <c r="E12" s="58" t="n"/>
       <c r="F12" s="58" t="n"/>
       <c r="G12" s="56">
-        <f>IF(C12&amp;F12="","",IFERROR(VLOOKUP(C12&amp;"→"&amp;F12,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C12&amp;F12="","",IFERROR(VLOOKUP(C12&amp;"→"&amp;F12,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H12" s="59">
@@ -2794,7 +2801,7 @@
       <c r="E13" s="58" t="n"/>
       <c r="F13" s="58" t="n"/>
       <c r="G13" s="56">
-        <f>IF(C13&amp;F13="","",IFERROR(VLOOKUP(C13&amp;"→"&amp;F13,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C13&amp;F13="","",IFERROR(VLOOKUP(C13&amp;"→"&amp;F13,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H13" s="59">
@@ -2820,7 +2827,7 @@
       <c r="E14" s="58" t="n"/>
       <c r="F14" s="58" t="n"/>
       <c r="G14" s="56">
-        <f>IF(C14&amp;F14="","",IFERROR(VLOOKUP(C14&amp;"→"&amp;F14,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C14&amp;F14="","",IFERROR(VLOOKUP(C14&amp;"→"&amp;F14,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H14" s="59">
@@ -2846,7 +2853,7 @@
       <c r="E15" s="58" t="n"/>
       <c r="F15" s="58" t="n"/>
       <c r="G15" s="56">
-        <f>IF(C15&amp;F15="","",IFERROR(VLOOKUP(C15&amp;"→"&amp;F15,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C15&amp;F15="","",IFERROR(VLOOKUP(C15&amp;"→"&amp;F15,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H15" s="59">
@@ -2871,7 +2878,7 @@
       <c r="E16" s="58" t="n"/>
       <c r="F16" s="58" t="n"/>
       <c r="G16" s="56">
-        <f>IF(C16&amp;F16="","",IFERROR(VLOOKUP(C16&amp;"→"&amp;F16,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C16&amp;F16="","",IFERROR(VLOOKUP(C16&amp;"→"&amp;F16,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H16" s="59">
@@ -2895,7 +2902,7 @@
       <c r="E17" s="58" t="n"/>
       <c r="F17" s="58" t="n"/>
       <c r="G17" s="56">
-        <f>IF(C17&amp;F17="","",IFERROR(VLOOKUP(C17&amp;"→"&amp;F17,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C17&amp;F17="","",IFERROR(VLOOKUP(C17&amp;"→"&amp;F17,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H17" s="59">
@@ -2919,7 +2926,7 @@
       <c r="E18" s="58" t="n"/>
       <c r="F18" s="58" t="n"/>
       <c r="G18" s="56">
-        <f>IF(C18&amp;F18="","",IFERROR(VLOOKUP(C18&amp;"→"&amp;F18,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C18&amp;F18="","",IFERROR(VLOOKUP(C18&amp;"→"&amp;F18,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H18" s="59">
@@ -2943,7 +2950,7 @@
       <c r="E19" s="58" t="n"/>
       <c r="F19" s="58" t="n"/>
       <c r="G19" s="56">
-        <f>IF(C19&amp;F19="","",IFERROR(VLOOKUP(C19&amp;"→"&amp;F19,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C19&amp;F19="","",IFERROR(VLOOKUP(C19&amp;"→"&amp;F19,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H19" s="59">
@@ -2967,7 +2974,7 @@
       <c r="E20" s="58" t="n"/>
       <c r="F20" s="58" t="n"/>
       <c r="G20" s="56">
-        <f>IF(C20&amp;F20="","",IFERROR(VLOOKUP(C20&amp;"→"&amp;F20,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C20&amp;F20="","",IFERROR(VLOOKUP(C20&amp;"→"&amp;F20,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H20" s="59">
@@ -2991,7 +2998,7 @@
       <c r="E21" s="58" t="n"/>
       <c r="F21" s="58" t="n"/>
       <c r="G21" s="56">
-        <f>IF(C21&amp;F21="","",IFERROR(VLOOKUP(C21&amp;"→"&amp;F21,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C21&amp;F21="","",IFERROR(VLOOKUP(C21&amp;"→"&amp;F21,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H21" s="59">
@@ -3255,23 +3262,23 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="18">
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="A23:I23"/>
     <mergeCell ref="A25:I25"/>
-    <mergeCell ref="L8:M9"/>
-    <mergeCell ref="A33:I33"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="A37:I37"/>
-    <mergeCell ref="L15:M15"/>
-    <mergeCell ref="A27:I27"/>
-    <mergeCell ref="A23:I23"/>
     <mergeCell ref="A34:I34"/>
     <mergeCell ref="A30:I30"/>
     <mergeCell ref="A31:H31"/>
     <mergeCell ref="A36:H36"/>
+    <mergeCell ref="L8:M9"/>
     <mergeCell ref="A32:I32"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A26:H26"/>
     <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A33:I33"/>
     <mergeCell ref="A24:H24"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="A27:I27"/>
     <mergeCell ref="A1:J1"/>
   </mergeCells>
   <conditionalFormatting sqref="G5:G21">
@@ -3434,7 +3441,7 @@
         </is>
       </c>
       <c r="G5" s="56">
-        <f>IF(C5&amp;F5="","",IFERROR(VLOOKUP(C5&amp;"→"&amp;F5,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C5&amp;F5="","",IFERROR(VLOOKUP(C5&amp;"→"&amp;F5,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H5" s="57" t="n">
@@ -3479,7 +3486,7 @@
         </is>
       </c>
       <c r="G6" s="56">
-        <f>IF(C6&amp;F6="","",IFERROR(VLOOKUP(C6&amp;"→"&amp;F6,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C6&amp;F6="","",IFERROR(VLOOKUP(C6&amp;"→"&amp;F6,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>12.0</v>
       </c>
       <c r="H6" s="57" t="n">
@@ -3524,7 +3531,7 @@
         </is>
       </c>
       <c r="G7" s="56">
-        <f>IF(C7&amp;F7="","",IFERROR(VLOOKUP(C7&amp;"→"&amp;F7,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C7&amp;F7="","",IFERROR(VLOOKUP(C7&amp;"→"&amp;F7,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H7" s="57" t="n">
@@ -3569,7 +3576,7 @@
         </is>
       </c>
       <c r="G8" s="56">
-        <f>IF(C8&amp;F8="","",IFERROR(VLOOKUP(C8&amp;"→"&amp;F8,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C8&amp;F8="","",IFERROR(VLOOKUP(C8&amp;"→"&amp;F8,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H8" s="57" t="n">
@@ -3620,7 +3627,7 @@
         </is>
       </c>
       <c r="G9" s="56">
-        <f>IF(C9&amp;F9="","",IFERROR(VLOOKUP(C9&amp;"→"&amp;F9,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C9&amp;F9="","",IFERROR(VLOOKUP(C9&amp;"→"&amp;F9,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H9" s="57" t="n">
@@ -3665,7 +3672,7 @@
         </is>
       </c>
       <c r="G10" s="56">
-        <f>IF(C10&amp;F10="","",IFERROR(VLOOKUP(C10&amp;"→"&amp;F10,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C10&amp;F10="","",IFERROR(VLOOKUP(C10&amp;"→"&amp;F10,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H10" s="57" t="n">
@@ -3690,7 +3697,7 @@
       <c r="E11" s="58" t="n"/>
       <c r="F11" s="58" t="n"/>
       <c r="G11" s="56">
-        <f>IF(C11&amp;F11="","",IFERROR(VLOOKUP(C11&amp;"→"&amp;F11,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C11&amp;F11="","",IFERROR(VLOOKUP(C11&amp;"→"&amp;F11,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H11" s="59">
@@ -3716,7 +3723,7 @@
       <c r="E12" s="58" t="n"/>
       <c r="F12" s="58" t="n"/>
       <c r="G12" s="56">
-        <f>IF(C12&amp;F12="","",IFERROR(VLOOKUP(C12&amp;"→"&amp;F12,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C12&amp;F12="","",IFERROR(VLOOKUP(C12&amp;"→"&amp;F12,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H12" s="59">
@@ -3742,7 +3749,7 @@
       <c r="E13" s="58" t="n"/>
       <c r="F13" s="58" t="n"/>
       <c r="G13" s="56">
-        <f>IF(C13&amp;F13="","",IFERROR(VLOOKUP(C13&amp;"→"&amp;F13,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C13&amp;F13="","",IFERROR(VLOOKUP(C13&amp;"→"&amp;F13,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H13" s="59">
@@ -3768,7 +3775,7 @@
       <c r="E14" s="58" t="n"/>
       <c r="F14" s="58" t="n"/>
       <c r="G14" s="56">
-        <f>IF(C14&amp;F14="","",IFERROR(VLOOKUP(C14&amp;"→"&amp;F14,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C14&amp;F14="","",IFERROR(VLOOKUP(C14&amp;"→"&amp;F14,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H14" s="59">
@@ -3794,7 +3801,7 @@
       <c r="E15" s="58" t="n"/>
       <c r="F15" s="58" t="n"/>
       <c r="G15" s="56">
-        <f>IF(C15&amp;F15="","",IFERROR(VLOOKUP(C15&amp;"→"&amp;F15,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C15&amp;F15="","",IFERROR(VLOOKUP(C15&amp;"→"&amp;F15,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H15" s="59">
@@ -3819,7 +3826,7 @@
       <c r="E16" s="58" t="n"/>
       <c r="F16" s="58" t="n"/>
       <c r="G16" s="56">
-        <f>IF(C16&amp;F16="","",IFERROR(VLOOKUP(C16&amp;"→"&amp;F16,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C16&amp;F16="","",IFERROR(VLOOKUP(C16&amp;"→"&amp;F16,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H16" s="59">
@@ -3844,7 +3851,7 @@
       <c r="E17" s="58" t="n"/>
       <c r="F17" s="58" t="n"/>
       <c r="G17" s="56">
-        <f>IF(C17&amp;F17="","",IFERROR(VLOOKUP(C17&amp;"→"&amp;F17,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C17&amp;F17="","",IFERROR(VLOOKUP(C17&amp;"→"&amp;F17,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H17" s="59">
@@ -3869,7 +3876,7 @@
       <c r="E18" s="58" t="n"/>
       <c r="F18" s="58" t="n"/>
       <c r="G18" s="56">
-        <f>IF(C18&amp;F18="","",IFERROR(VLOOKUP(C18&amp;"→"&amp;F18,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C18&amp;F18="","",IFERROR(VLOOKUP(C18&amp;"→"&amp;F18,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H18" s="59">
@@ -3894,7 +3901,7 @@
       <c r="E19" s="58" t="n"/>
       <c r="F19" s="58" t="n"/>
       <c r="G19" s="56">
-        <f>IF(C19&amp;F19="","",IFERROR(VLOOKUP(C19&amp;"→"&amp;F19,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C19&amp;F19="","",IFERROR(VLOOKUP(C19&amp;"→"&amp;F19,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H19" s="59">
@@ -3919,7 +3926,7 @@
       <c r="E20" s="58" t="n"/>
       <c r="F20" s="58" t="n"/>
       <c r="G20" s="56">
-        <f>IF(C20&amp;F20="","",IFERROR(VLOOKUP(C20&amp;"→"&amp;F20,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C20&amp;F20="","",IFERROR(VLOOKUP(C20&amp;"→"&amp;F20,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H20" s="59">
@@ -4185,23 +4192,23 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="18">
     <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A32:I32"/>
     <mergeCell ref="L8:M9"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A35:H35"/>
     <mergeCell ref="A31:I31"/>
     <mergeCell ref="A33:I33"/>
     <mergeCell ref="A36:I36"/>
     <mergeCell ref="L3:M3"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A25:H25"/>
     <mergeCell ref="A29:I29"/>
-    <mergeCell ref="A26:I26"/>
-    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A24:I24"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A28:H28"/>
-    <mergeCell ref="A32:I32"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="A35:H35"/>
-    <mergeCell ref="A22:I22"/>
-    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <conditionalFormatting sqref="G5:G20">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
@@ -4363,7 +4370,7 @@
         </is>
       </c>
       <c r="G5" s="56">
-        <f>IF(C5&amp;F5="","",IFERROR(VLOOKUP(C5&amp;"→"&amp;F5,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C5&amp;F5="","",IFERROR(VLOOKUP(C5&amp;"→"&amp;F5,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H5" s="57" t="n">
@@ -4408,7 +4415,7 @@
         </is>
       </c>
       <c r="G6" s="56">
-        <f>IF(C6&amp;F6="","",IFERROR(VLOOKUP(C6&amp;"→"&amp;F6,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C6&amp;F6="","",IFERROR(VLOOKUP(C6&amp;"→"&amp;F6,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H6" s="57" t="n">
@@ -4453,7 +4460,7 @@
         </is>
       </c>
       <c r="G7" s="56">
-        <f>IF(C7&amp;F7="","",IFERROR(VLOOKUP(C7&amp;"→"&amp;F7,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C7&amp;F7="","",IFERROR(VLOOKUP(C7&amp;"→"&amp;F7,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H7" s="57" t="n">
@@ -4498,7 +4505,7 @@
         </is>
       </c>
       <c r="G8" s="56">
-        <f>IF(C8&amp;F8="","",IFERROR(VLOOKUP(C8&amp;"→"&amp;F8,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C8&amp;F8="","",IFERROR(VLOOKUP(C8&amp;"→"&amp;F8,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>12.0</v>
       </c>
       <c r="H8" s="57" t="n">
@@ -4549,7 +4556,7 @@
         </is>
       </c>
       <c r="G9" s="56">
-        <f>IF(C9&amp;F9="","",IFERROR(VLOOKUP(C9&amp;"→"&amp;F9,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C9&amp;F9="","",IFERROR(VLOOKUP(C9&amp;"→"&amp;F9,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H9" s="57" t="n">
@@ -4594,7 +4601,7 @@
         </is>
       </c>
       <c r="G10" s="56">
-        <f>IF(C10&amp;F10="","",IFERROR(VLOOKUP(C10&amp;"→"&amp;F10,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C10&amp;F10="","",IFERROR(VLOOKUP(C10&amp;"→"&amp;F10,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H10" s="57" t="n">
@@ -4639,7 +4646,7 @@
         </is>
       </c>
       <c r="G11" s="56">
-        <f>IF(C11&amp;F11="","",IFERROR(VLOOKUP(C11&amp;"→"&amp;F11,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C11&amp;F11="","",IFERROR(VLOOKUP(C11&amp;"→"&amp;F11,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H11" s="57" t="n">
@@ -4684,7 +4691,7 @@
         </is>
       </c>
       <c r="G12" s="56">
-        <f>IF(C12&amp;F12="","",IFERROR(VLOOKUP(C12&amp;"→"&amp;F12,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C12&amp;F12="","",IFERROR(VLOOKUP(C12&amp;"→"&amp;F12,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H12" s="59" t="n">
@@ -4729,7 +4736,7 @@
         </is>
       </c>
       <c r="G13" s="56">
-        <f>IF(C13&amp;F13="","",IFERROR(VLOOKUP(C13&amp;"→"&amp;F13,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C13&amp;F13="","",IFERROR(VLOOKUP(C13&amp;"→"&amp;F13,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H13" s="59" t="n">
@@ -4774,7 +4781,7 @@
         </is>
       </c>
       <c r="G14" s="56">
-        <f>IF(C14&amp;F14="","",IFERROR(VLOOKUP(C14&amp;"→"&amp;F14,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C14&amp;F14="","",IFERROR(VLOOKUP(C14&amp;"→"&amp;F14,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v>1.0</v>
       </c>
       <c r="H14" s="59" t="n">
@@ -4799,7 +4806,7 @@
       <c r="E15" s="58" t="n"/>
       <c r="F15" s="58" t="n"/>
       <c r="G15" s="56">
-        <f>IF(C15&amp;F15="","",IFERROR(VLOOKUP(C15&amp;"→"&amp;F15,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C15&amp;F15="","",IFERROR(VLOOKUP(C15&amp;"→"&amp;F15,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H15" s="59">
@@ -4824,7 +4831,7 @@
       <c r="E16" s="58" t="n"/>
       <c r="F16" s="58" t="n"/>
       <c r="G16" s="56">
-        <f>IF(C16&amp;F16="","",IFERROR(VLOOKUP(C16&amp;"→"&amp;F16,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C16&amp;F16="","",IFERROR(VLOOKUP(C16&amp;"→"&amp;F16,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H16" s="59">
@@ -4848,7 +4855,7 @@
       <c r="E17" s="58" t="n"/>
       <c r="F17" s="58" t="n"/>
       <c r="G17" s="56">
-        <f>IF(C17&amp;F17="","",IFERROR(VLOOKUP(C17&amp;"→"&amp;F17,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C17&amp;F17="","",IFERROR(VLOOKUP(C17&amp;"→"&amp;F17,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H17" s="59">
@@ -4872,7 +4879,7 @@
       <c r="E18" s="58" t="n"/>
       <c r="F18" s="58" t="n"/>
       <c r="G18" s="56">
-        <f>IF(C18&amp;F18="","",IFERROR(VLOOKUP(C18&amp;"→"&amp;F18,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C18&amp;F18="","",IFERROR(VLOOKUP(C18&amp;"→"&amp;F18,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H18" s="59">
@@ -4896,7 +4903,7 @@
       <c r="E19" s="58" t="n"/>
       <c r="F19" s="58" t="n"/>
       <c r="G19" s="56">
-        <f>IF(C19&amp;F19="","",IFERROR(VLOOKUP(C19&amp;"→"&amp;F19,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C19&amp;F19="","",IFERROR(VLOOKUP(C19&amp;"→"&amp;F19,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H19" s="59">
@@ -4920,7 +4927,7 @@
       <c r="E20" s="58" t="n"/>
       <c r="F20" s="58" t="n"/>
       <c r="G20" s="56">
-        <f>IF(C20&amp;F20="","",IFERROR(VLOOKUP(C20&amp;"→"&amp;F20,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C20&amp;F20="","",IFERROR(VLOOKUP(C20&amp;"→"&amp;F20,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H20" s="59">
@@ -4944,7 +4951,7 @@
       <c r="E21" s="58" t="n"/>
       <c r="F21" s="58" t="n"/>
       <c r="G21" s="56">
-        <f>IF(C21&amp;F21="","",IFERROR(VLOOKUP(C21&amp;"→"&amp;F21,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <f>IF(C21&amp;F21="","",IFERROR(VLOOKUP(C21&amp;"→"&amp;F21,Conversiones!$A$5:$B$67,2,FALSE),"?"))</f>
         <v/>
       </c>
       <c r="H21" s="59">
@@ -5208,23 +5215,23 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="18">
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="A23:I23"/>
     <mergeCell ref="A25:I25"/>
-    <mergeCell ref="L8:M9"/>
-    <mergeCell ref="A33:I33"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="A37:I37"/>
-    <mergeCell ref="L15:M15"/>
-    <mergeCell ref="A27:I27"/>
-    <mergeCell ref="A23:I23"/>
     <mergeCell ref="A34:I34"/>
     <mergeCell ref="A30:I30"/>
     <mergeCell ref="A31:H31"/>
     <mergeCell ref="A36:H36"/>
+    <mergeCell ref="L8:M9"/>
     <mergeCell ref="A32:I32"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A26:H26"/>
     <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A33:I33"/>
     <mergeCell ref="A24:H24"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="A27:I27"/>
     <mergeCell ref="A1:J1"/>
   </mergeCells>
   <conditionalFormatting sqref="G5:G21">
@@ -5264,7 +5271,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5282,7 +5289,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>La usa la columna «Factor» de cada escandallo. Puedes añadir parejas al final: la clave se escribe «compra→uso».</t>
+          <t>La usa la columna «Factor» de cada escandallo. Puedes añadir parejas al final, hasta la fila 67: la clave se escribe «compra→uso».</t>
         </is>
       </c>
     </row>
@@ -5799,6 +5806,7 @@
         </is>
       </c>
     </row>
+    <row r="38"/>
   </sheetData>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -5842,7 +5850,13 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Mide tu merma real con la plantilla 12 (Test de Rendimiento) y llévala a «Merma (%)» de la ficha.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="66" t="inlineStr">
         <is>
